--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_ThanhTamNhaTrang_010626.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_ThanhTamNhaTrang_010626.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t xml:space="preserve">
 </t>
@@ -60,7 +60,7 @@
     <t>Phòngban/ Bộ phận: PKT/ Bảo hành - Sản xuất…..</t>
   </si>
   <si>
-    <t xml:space="preserve">Tên Khách hàng: Đai lý Thành Tâm Nha Trang </t>
+    <t xml:space="preserve">Tên Khách hàng: Đại lý Thành Tâm Nha Trang </t>
   </si>
   <si>
     <t>STT</t>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>ID: 00320007F6, xuất kho ngày 11/03/2026, giữ lại bo mạch lỗi tận dụng linh kiện sửa chữa</t>
-  </si>
-  <si>
-    <t>Tổng</t>
   </si>
   <si>
     <t>TP. KTTH</t>
@@ -142,7 +139,7 @@
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -374,13 +371,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -989,11 +979,11 @@
     <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1081,22 +1071,19 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1717,174 +1704,169 @@
       <c r="A10" s="31">
         <v>1</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="32" t="s">
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:8">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:8">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:8">
+      <c r="A13" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35">
-        <f>SUM(F10:F10)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:8">
-      <c r="A13" s="39" t="s">
+      <c r="B13" s="38"/>
+      <c r="C13" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40" t="s">
+      <c r="D13" s="39"/>
+      <c r="E13" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40" t="s">
+      <c r="F13" s="39"/>
+      <c r="G13" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40" t="s">
+      <c r="H13" s="39"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A14" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="40"/>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A14" s="41" t="s">
+      <c r="B14" s="40"/>
+      <c r="C14" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:8">
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="36"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:8">
+      <c r="A16" s="36"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="36"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:8">
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="36"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:8">
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:8">
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="36"/>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:8">
+      <c r="A20" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="42"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:8">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="37"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:8">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="37"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:8">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="37"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:8">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:8">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="37"/>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="45" t="s">
+      <c r="B20" s="44"/>
+      <c r="C20" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="40" t="s">
+      <c r="D20" s="39"/>
+      <c r="E20" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40" t="s">
+      <c r="F20" s="39"/>
+      <c r="G20" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="40"/>
+      <c r="H20" s="39"/>
     </row>
     <row r="21" s="2" customFormat="1"/>
     <row r="22" s="2" customFormat="1" spans="1:8">
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
     </row>
     <row r="23" s="2" customFormat="1"/>
     <row r="24" s="2" customFormat="1"/>
     <row r="25" s="2" customFormat="1"/>
     <row r="26" s="2" customFormat="1" spans="1:8">
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
     </row>
     <row r="27" s="2" customFormat="1"/>
     <row r="28" s="2" customFormat="1"/>
     <row r="33" ht="15.75" spans="8:8">
-      <c r="H33" s="48"/>
+      <c r="H33" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_ThanhTamNhaTrang_010626.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_ThanhTamNhaTrang_010626.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t xml:space="preserve">
 </t>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>ID: 00320007F6, xuất kho ngày 11/03/2026, giữ lại bo mạch lỗi tận dụng linh kiện sửa chữa</t>
+  </si>
+  <si>
+    <t>NOTE: Hủy phiếu trả mạch lại cho kho</t>
   </si>
   <si>
     <t>TP. KTTH</t>
@@ -139,7 +142,7 @@
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -200,6 +203,19 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -835,28 +851,19 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -865,125 +872,134 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1089,6 +1105,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1098,16 +1120,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1116,7 +1138,7 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1734,49 +1756,51 @@
     </row>
     <row r="12" s="2" customFormat="1" spans="1:8">
       <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
+      <c r="B12" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:8">
-      <c r="A13" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="39" t="s">
+      <c r="A13" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39" t="s">
+      <c r="B13" s="40"/>
+      <c r="C13" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39" t="s">
+      <c r="D13" s="41"/>
+      <c r="E13" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="41"/>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A14" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="41"/>
+      <c r="A14" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="43"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:8">
       <c r="A15" s="36"/>
@@ -1785,7 +1809,7 @@
       <c r="D15" s="36"/>
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
-      <c r="G15" s="42"/>
+      <c r="G15" s="44"/>
       <c r="H15" s="36"/>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:8">
@@ -1795,17 +1819,17 @@
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="42"/>
+      <c r="G16" s="44"/>
       <c r="H16" s="36"/>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:8">
       <c r="A17" s="36"/>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="42"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="36"/>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:8">
@@ -1825,48 +1849,48 @@
       <c r="D19" s="36"/>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="42"/>
+      <c r="G19" s="44"/>
       <c r="H19" s="36"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="39" t="s">
+      <c r="A20" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39" t="s">
+      <c r="B20" s="46"/>
+      <c r="C20" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39" t="s">
+      <c r="D20" s="41"/>
+      <c r="E20" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" s="2" customFormat="1"/>
     <row r="22" s="2" customFormat="1" spans="1:8">
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
     </row>
     <row r="23" s="2" customFormat="1"/>
     <row r="24" s="2" customFormat="1"/>
     <row r="25" s="2" customFormat="1"/>
     <row r="26" s="2" customFormat="1" spans="1:8">
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
     </row>
     <row r="27" s="2" customFormat="1"/>
     <row r="28" s="2" customFormat="1"/>
     <row r="33" ht="15.75" spans="8:8">
-      <c r="H33" s="47"/>
+      <c r="H33" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="19">
